--- a/src/data/OpenCartTestData.xlsx
+++ b/src/data/OpenCartTestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hussa\Documents\SDET\MyProjects\MyOpenCartPWFramework\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68879744-A8D6-4A6A-A83B-2D1C2CA0615A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEFB42F-33F5-48DB-94A3-3BD8280B8D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6468" yWindow="624" windowWidth="15612" windowHeight="11112" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>username</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>pwbatchtest@open.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -107,10 +110,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -402,15 +404,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -418,16 +420,20 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
